--- a/outputs_xlsx_solution/test33.2-wide.xlsx
+++ b/outputs_xlsx_solution/test33.2-wide.xlsx
@@ -68,6 +68,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fld F21, 120(X0)</t>
   </si>
   <si>
@@ -207,6 +210,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -882,7 +888,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -902,13 +908,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -928,13 +934,13 @@
         <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -954,16 +960,16 @@
         <v>7</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -974,7 +980,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -983,16 +989,16 @@
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" t="s">
         <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -1003,7 +1009,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -1012,16 +1018,16 @@
         <v>7</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7" t="s">
         <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -1032,7 +1038,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
         <v>5</v>
@@ -1044,10 +1050,10 @@
         <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -1058,7 +1064,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
         <v>5</v>
@@ -1070,10 +1076,10 @@
         <v>10</v>
       </c>
       <c r="L9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -1084,7 +1090,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
@@ -1093,13 +1099,13 @@
         <v>7</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L10" t="s">
         <v>10</v>
       </c>
       <c r="M10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -1110,7 +1116,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
@@ -1128,7 +1134,7 @@
         <v>10</v>
       </c>
       <c r="O11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -1139,7 +1145,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s">
         <v>5</v>
@@ -1148,7 +1154,7 @@
         <v>7</v>
       </c>
       <c r="L12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O12" t="s">
         <v>10</v>
@@ -1160,7 +1166,7 @@
         <v>10</v>
       </c>
       <c r="R12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -1171,7 +1177,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" t="s">
         <v>5</v>
@@ -1180,7 +1186,7 @@
         <v>7</v>
       </c>
       <c r="M13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -1195,7 +1201,7 @@
         <v>10</v>
       </c>
       <c r="V13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -1206,7 +1212,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J14" t="s">
         <v>5</v>
@@ -1227,10 +1233,10 @@
         <v>10</v>
       </c>
       <c r="Q14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -1241,7 +1247,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J15" t="s">
         <v>5</v>
@@ -1268,10 +1274,10 @@
         <v>10</v>
       </c>
       <c r="T15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -1282,7 +1288,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -1294,10 +1300,10 @@
         <v>10</v>
       </c>
       <c r="O16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1308,7 +1314,7 @@
         <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
@@ -1320,10 +1326,10 @@
         <v>10</v>
       </c>
       <c r="P17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1334,7 +1340,7 @@
         <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L18" t="s">
         <v>5</v>
@@ -1346,10 +1352,10 @@
         <v>10</v>
       </c>
       <c r="P18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -1360,7 +1366,7 @@
         <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L19" t="s">
         <v>5</v>
@@ -1369,16 +1375,16 @@
         <v>7</v>
       </c>
       <c r="P19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q19" t="s">
         <v>10</v>
       </c>
       <c r="R19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1389,7 +1395,7 @@
         <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M20" t="s">
         <v>5</v>
@@ -1398,10 +1404,22 @@
         <v>7</v>
       </c>
       <c r="P20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q20" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R20" t="s">
+        <v>11</v>
+      </c>
+      <c r="S20" t="s">
+        <v>11</v>
+      </c>
+      <c r="T20" t="s">
+        <v>11</v>
+      </c>
+      <c r="U20" t="s">
+        <v>11</v>
       </c>
       <c r="V20" t="s">
         <v>10</v>
@@ -1416,7 +1434,7 @@
         <v>10</v>
       </c>
       <c r="Z20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -1427,7 +1445,7 @@
         <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M21" t="s">
         <v>5</v>
@@ -1436,7 +1454,7 @@
         <v>7</v>
       </c>
       <c r="Q21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z21" t="s">
         <v>10</v>
@@ -1448,7 +1466,7 @@
         <v>10</v>
       </c>
       <c r="AC21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1459,7 +1477,7 @@
         <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N22" t="s">
         <v>5</v>
@@ -1468,13 +1486,13 @@
         <v>7</v>
       </c>
       <c r="R22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC22" t="s">
         <v>10</v>
       </c>
       <c r="AD22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1485,7 +1503,7 @@
         <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N23" t="s">
         <v>5</v>
@@ -1494,16 +1512,16 @@
         <v>7</v>
       </c>
       <c r="R23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S23" t="s">
         <v>10</v>
       </c>
       <c r="T23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -1514,7 +1532,7 @@
         <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O24" t="s">
         <v>5</v>
@@ -1523,16 +1541,16 @@
         <v>7</v>
       </c>
       <c r="S24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T24" t="s">
         <v>10</v>
       </c>
       <c r="U24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -1543,7 +1561,7 @@
         <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U25" t="s">
         <v>5</v>
@@ -1555,10 +1573,10 @@
         <v>10</v>
       </c>
       <c r="X25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -1569,7 +1587,7 @@
         <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U26" t="s">
         <v>5</v>
@@ -1578,7 +1596,13 @@
         <v>7</v>
       </c>
       <c r="W26" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="X26" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>11</v>
       </c>
       <c r="Z26" t="s">
         <v>10</v>
@@ -1593,10 +1617,10 @@
         <v>10</v>
       </c>
       <c r="AD26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -1607,7 +1631,7 @@
         <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="V27" t="s">
         <v>5</v>
@@ -1616,7 +1640,7 @@
         <v>7</v>
       </c>
       <c r="X27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD27" t="s">
         <v>10</v>
@@ -1628,7 +1652,7 @@
         <v>10</v>
       </c>
       <c r="AG27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1639,7 +1663,7 @@
         <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V28" t="s">
         <v>5</v>
@@ -1648,13 +1672,13 @@
         <v>7</v>
       </c>
       <c r="X28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG28" t="s">
         <v>10</v>
       </c>
       <c r="AH28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -1665,7 +1689,7 @@
         <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W29" t="s">
         <v>5</v>
@@ -1674,16 +1698,16 @@
         <v>7</v>
       </c>
       <c r="Y29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z29" t="s">
         <v>10</v>
       </c>
       <c r="AA29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -1694,7 +1718,7 @@
         <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W30" t="s">
         <v>5</v>
@@ -1703,16 +1727,16 @@
         <v>7</v>
       </c>
       <c r="Y30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA30" t="s">
         <v>10</v>
       </c>
       <c r="AB30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -1723,7 +1747,7 @@
         <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X31" t="s">
         <v>5</v>
@@ -1735,10 +1759,10 @@
         <v>10</v>
       </c>
       <c r="AA31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1749,7 +1773,7 @@
         <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X32" t="s">
         <v>5</v>
@@ -1758,7 +1782,16 @@
         <v>7</v>
       </c>
       <c r="Z32" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>11</v>
       </c>
       <c r="AD32" t="s">
         <v>10</v>
@@ -1773,10 +1806,10 @@
         <v>10</v>
       </c>
       <c r="AH32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -1787,7 +1820,7 @@
         <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y33" t="s">
         <v>5</v>
@@ -1796,7 +1829,7 @@
         <v>7</v>
       </c>
       <c r="AA33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH33" t="s">
         <v>10</v>
@@ -1808,7 +1841,7 @@
         <v>10</v>
       </c>
       <c r="AK33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -1819,7 +1852,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y34" t="s">
         <v>5</v>
@@ -1828,22 +1861,22 @@
         <v>7</v>
       </c>
       <c r="AA34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK34" t="s">
         <v>10</v>
       </c>
       <c r="AL34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -1854,7 +1887,7 @@
         <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z35" t="s">
         <v>5</v>
@@ -1863,16 +1896,16 @@
         <v>7</v>
       </c>
       <c r="AD35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE35" t="s">
         <v>10</v>
       </c>
       <c r="AF35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -1883,7 +1916,7 @@
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z36" t="s">
         <v>5</v>
@@ -1892,16 +1925,16 @@
         <v>7</v>
       </c>
       <c r="AE36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF36" t="s">
         <v>10</v>
       </c>
       <c r="AG36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -1912,7 +1945,7 @@
         <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AG37" t="s">
         <v>5</v>
@@ -1930,10 +1963,10 @@
         <v>10</v>
       </c>
       <c r="AL37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
@@ -1944,7 +1977,7 @@
         <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AG38" t="s">
         <v>5</v>
@@ -1953,7 +1986,7 @@
         <v>7</v>
       </c>
       <c r="AI38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL38" t="s">
         <v>10</v>
@@ -1965,7 +1998,7 @@
         <v>10</v>
       </c>
       <c r="AO38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -1976,7 +2009,7 @@
         <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AH39" t="s">
         <v>5</v>
@@ -1988,10 +2021,10 @@
         <v>10</v>
       </c>
       <c r="AK39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
@@ -2002,7 +2035,7 @@
         <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH40" t="s">
         <v>5</v>
@@ -2011,10 +2044,10 @@
         <v>10</v>
       </c>
       <c r="AK40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -2025,7 +2058,7 @@
         <v>36</v>
       </c>
       <c r="C41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI41" t="s">
         <v>5</v>
@@ -2043,10 +2076,10 @@
         <v>10</v>
       </c>
       <c r="AN41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -2057,7 +2090,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI42" t="s">
         <v>5</v>
@@ -2066,10 +2099,10 @@
         <v>7</v>
       </c>
       <c r="AK42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN42" t="s">
         <v>10</v>
@@ -2081,7 +2114,7 @@
         <v>10</v>
       </c>
       <c r="AQ42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -2092,7 +2125,7 @@
         <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ43" t="s">
         <v>5</v>
@@ -2101,7 +2134,10 @@
         <v>7</v>
       </c>
       <c r="AL43" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="AQ43" t="s">
+        <v>11</v>
       </c>
       <c r="AR43" t="s">
         <v>10</v>
@@ -2116,7 +2152,7 @@
         <v>10</v>
       </c>
       <c r="AV43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -2127,7 +2163,7 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ44" t="s">
         <v>5</v>
@@ -2148,13 +2184,13 @@
         <v>10</v>
       </c>
       <c r="AQ44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AR44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -2165,7 +2201,7 @@
         <v>52</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK45" t="s">
         <v>5</v>
@@ -2192,10 +2228,10 @@
         <v>10</v>
       </c>
       <c r="AS45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -2206,7 +2242,7 @@
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK46" t="s">
         <v>5</v>
@@ -2218,10 +2254,10 @@
         <v>10</v>
       </c>
       <c r="AO46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
@@ -2232,7 +2268,7 @@
         <v>60</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL47" t="s">
         <v>5</v>
@@ -2241,16 +2277,16 @@
         <v>7</v>
       </c>
       <c r="AN47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO47" t="s">
         <v>10</v>
       </c>
       <c r="AP47" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -2261,7 +2297,7 @@
         <v>64</v>
       </c>
       <c r="C48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL48" t="s">
         <v>5</v>
@@ -2273,10 +2309,10 @@
         <v>10</v>
       </c>
       <c r="AP48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -2287,7 +2323,7 @@
         <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM49" t="s">
         <v>5</v>
@@ -2296,16 +2332,16 @@
         <v>7</v>
       </c>
       <c r="AO49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP49" t="s">
         <v>10</v>
       </c>
       <c r="AQ49" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -2316,7 +2352,7 @@
         <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM50" t="s">
         <v>5</v>
@@ -2325,13 +2361,22 @@
         <v>7</v>
       </c>
       <c r="AP50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR50" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="AS50" t="s">
+        <v>11</v>
+      </c>
+      <c r="AT50" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU50" t="s">
+        <v>11</v>
       </c>
       <c r="AV50" t="s">
         <v>10</v>
@@ -2346,7 +2391,7 @@
         <v>10</v>
       </c>
       <c r="AZ50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51">
@@ -2357,7 +2402,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN51" t="s">
         <v>5</v>
@@ -2366,7 +2411,7 @@
         <v>7</v>
       </c>
       <c r="AR51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ51" t="s">
         <v>10</v>
@@ -2378,7 +2423,7 @@
         <v>10</v>
       </c>
       <c r="BC51" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
@@ -2389,7 +2434,7 @@
         <v>80</v>
       </c>
       <c r="C52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AN52" t="s">
         <v>5</v>
@@ -2398,13 +2443,13 @@
         <v>7</v>
       </c>
       <c r="AS52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC52" t="s">
         <v>10</v>
       </c>
       <c r="BD52" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
@@ -2415,7 +2460,7 @@
         <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AO53" t="s">
         <v>5</v>
@@ -2424,16 +2469,16 @@
         <v>7</v>
       </c>
       <c r="AS53" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT53" t="s">
         <v>10</v>
       </c>
       <c r="AU53" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD53" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -2444,7 +2489,7 @@
         <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AO54" t="s">
         <v>5</v>
@@ -2453,16 +2498,16 @@
         <v>7</v>
       </c>
       <c r="AT54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU54" t="s">
         <v>10</v>
       </c>
       <c r="AV54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE54" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
@@ -2473,7 +2518,7 @@
         <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP55" t="s">
         <v>5</v>
@@ -2482,16 +2527,16 @@
         <v>7</v>
       </c>
       <c r="AT55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU55" t="s">
         <v>10</v>
       </c>
       <c r="AV55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE55" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
@@ -2502,7 +2547,7 @@
         <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP56" t="s">
         <v>5</v>
@@ -2511,10 +2556,19 @@
         <v>7</v>
       </c>
       <c r="AU56" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV56" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="AW56" t="s">
+        <v>11</v>
+      </c>
+      <c r="AX56" t="s">
+        <v>11</v>
+      </c>
+      <c r="AY56" t="s">
+        <v>11</v>
       </c>
       <c r="AZ56" t="s">
         <v>10</v>
@@ -2529,10 +2583,10 @@
         <v>10</v>
       </c>
       <c r="BD56" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF56" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -2543,7 +2597,7 @@
         <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ57" t="s">
         <v>5</v>
@@ -2552,7 +2606,7 @@
         <v>7</v>
       </c>
       <c r="AV57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD57" t="s">
         <v>10</v>
@@ -2564,7 +2618,7 @@
         <v>10</v>
       </c>
       <c r="BG57" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -2575,7 +2629,7 @@
         <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AQ58" t="s">
         <v>5</v>
@@ -2584,13 +2638,13 @@
         <v>7</v>
       </c>
       <c r="AW58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG58" t="s">
         <v>10</v>
       </c>
       <c r="BH58" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -2601,7 +2655,7 @@
         <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AR59" t="s">
         <v>5</v>
@@ -2610,16 +2664,16 @@
         <v>7</v>
       </c>
       <c r="AW59" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX59" t="s">
         <v>10</v>
       </c>
       <c r="AY59" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH59" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
@@ -2630,7 +2684,7 @@
         <v>88</v>
       </c>
       <c r="C60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AR60" t="s">
         <v>5</v>
@@ -2639,16 +2693,16 @@
         <v>7</v>
       </c>
       <c r="AX60" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY60" t="s">
         <v>10</v>
       </c>
       <c r="AZ60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BI60" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
@@ -2659,7 +2713,7 @@
         <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS61" t="s">
         <v>5</v>
@@ -2671,10 +2725,10 @@
         <v>10</v>
       </c>
       <c r="AY61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BI61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
@@ -2685,7 +2739,7 @@
         <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS62" t="s">
         <v>5</v>
@@ -2694,10 +2748,19 @@
         <v>7</v>
       </c>
       <c r="AY62" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ62" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="BA62" t="s">
+        <v>11</v>
+      </c>
+      <c r="BB62" t="s">
+        <v>11</v>
+      </c>
+      <c r="BC62" t="s">
+        <v>11</v>
       </c>
       <c r="BD62" t="s">
         <v>10</v>
@@ -2712,10 +2775,10 @@
         <v>10</v>
       </c>
       <c r="BH62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BJ62" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
@@ -2726,7 +2789,7 @@
         <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT63" t="s">
         <v>5</v>
@@ -2735,7 +2798,7 @@
         <v>7</v>
       </c>
       <c r="AZ63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH63" t="s">
         <v>10</v>
@@ -2747,7 +2810,7 @@
         <v>10</v>
       </c>
       <c r="BK63" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -2758,7 +2821,7 @@
         <v>80</v>
       </c>
       <c r="C64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AT64" t="s">
         <v>5</v>
@@ -2767,22 +2830,22 @@
         <v>7</v>
       </c>
       <c r="BA64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BK64" t="s">
         <v>10</v>
       </c>
       <c r="BL64" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
@@ -2793,7 +2856,7 @@
         <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AV65" t="s">
         <v>5</v>
@@ -2802,16 +2865,16 @@
         <v>7</v>
       </c>
       <c r="BD65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE65" t="s">
         <v>10</v>
       </c>
       <c r="BF65" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BL65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66">
@@ -2822,7 +2885,7 @@
         <v>88</v>
       </c>
       <c r="C66" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AV66" t="s">
         <v>5</v>
@@ -2831,16 +2894,16 @@
         <v>7</v>
       </c>
       <c r="BE66" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BF66" t="s">
         <v>10</v>
       </c>
       <c r="BG66" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BM66" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67">
@@ -2851,7 +2914,7 @@
         <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BG67" t="s">
         <v>5</v>
@@ -2869,10 +2932,10 @@
         <v>10</v>
       </c>
       <c r="BL67" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BM67" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
@@ -2883,7 +2946,7 @@
         <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BG68" t="s">
         <v>5</v>
@@ -2892,7 +2955,7 @@
         <v>7</v>
       </c>
       <c r="BI68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BL68" t="s">
         <v>10</v>
@@ -2904,7 +2967,7 @@
         <v>10</v>
       </c>
       <c r="BO68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
@@ -2915,7 +2978,7 @@
         <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BH69" t="s">
         <v>5</v>
@@ -2927,10 +2990,10 @@
         <v>10</v>
       </c>
       <c r="BK69" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BO69" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
@@ -2941,7 +3004,7 @@
         <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BH70" t="s">
         <v>5</v>
@@ -2953,10 +3016,10 @@
         <v>10</v>
       </c>
       <c r="BK70" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BP70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71">
@@ -2967,7 +3030,7 @@
         <v>36</v>
       </c>
       <c r="C71" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BI71" t="s">
         <v>5</v>
@@ -2985,10 +3048,10 @@
         <v>10</v>
       </c>
       <c r="BN71" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BP71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72">
@@ -2999,7 +3062,7 @@
         <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BI72" t="s">
         <v>5</v>
@@ -3008,10 +3071,10 @@
         <v>7</v>
       </c>
       <c r="BK72" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BL72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BN72" t="s">
         <v>10</v>
@@ -3023,7 +3086,7 @@
         <v>10</v>
       </c>
       <c r="BQ72" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73">
@@ -3034,7 +3097,7 @@
         <v>44</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BJ73" t="s">
         <v>5</v>
@@ -3043,7 +3106,10 @@
         <v>7</v>
       </c>
       <c r="BL73" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="BQ73" t="s">
+        <v>11</v>
       </c>
       <c r="BR73" t="s">
         <v>10</v>
@@ -3058,7 +3124,7 @@
         <v>10</v>
       </c>
       <c r="BV73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74">
@@ -3069,7 +3135,7 @@
         <v>48</v>
       </c>
       <c r="C74" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BJ74" t="s">
         <v>5</v>
@@ -3090,13 +3156,13 @@
         <v>10</v>
       </c>
       <c r="BQ74" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BR74" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BV74" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75">
@@ -3107,7 +3173,7 @@
         <v>52</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BK75" t="s">
         <v>5</v>
@@ -3134,10 +3200,10 @@
         <v>10</v>
       </c>
       <c r="BS75" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW75" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76">
@@ -3148,7 +3214,7 @@
         <v>56</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BK76" t="s">
         <v>5</v>
@@ -3160,10 +3226,10 @@
         <v>10</v>
       </c>
       <c r="BO76" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW76" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77">
@@ -3174,7 +3240,7 @@
         <v>60</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BL77" t="s">
         <v>5</v>
@@ -3183,16 +3249,16 @@
         <v>7</v>
       </c>
       <c r="BN77" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BO77" t="s">
         <v>10</v>
       </c>
       <c r="BP77" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78">
@@ -3203,7 +3269,7 @@
         <v>64</v>
       </c>
       <c r="C78" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BL78" t="s">
         <v>5</v>
@@ -3215,10 +3281,10 @@
         <v>10</v>
       </c>
       <c r="BP78" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX78" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79">
@@ -3229,7 +3295,7 @@
         <v>68</v>
       </c>
       <c r="C79" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BM79" t="s">
         <v>5</v>
@@ -3238,16 +3304,16 @@
         <v>7</v>
       </c>
       <c r="BO79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BP79" t="s">
         <v>10</v>
       </c>
       <c r="BQ79" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BY79" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80">
@@ -3258,7 +3324,7 @@
         <v>72</v>
       </c>
       <c r="C80" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BM80" t="s">
         <v>5</v>
@@ -3267,13 +3333,22 @@
         <v>7</v>
       </c>
       <c r="BP80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BQ80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BR80" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="BS80" t="s">
+        <v>11</v>
+      </c>
+      <c r="BT80" t="s">
+        <v>11</v>
+      </c>
+      <c r="BU80" t="s">
+        <v>11</v>
       </c>
       <c r="BV80" t="s">
         <v>10</v>
@@ -3288,7 +3363,7 @@
         <v>10</v>
       </c>
       <c r="BZ80" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81">
@@ -3299,7 +3374,7 @@
         <v>76</v>
       </c>
       <c r="C81" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BN81" t="s">
         <v>5</v>
@@ -3308,7 +3383,7 @@
         <v>7</v>
       </c>
       <c r="BR81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BZ81" t="s">
         <v>10</v>
@@ -3320,7 +3395,7 @@
         <v>10</v>
       </c>
       <c r="CC81" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82">
@@ -3331,7 +3406,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BN82" t="s">
         <v>5</v>
@@ -3340,13 +3415,13 @@
         <v>7</v>
       </c>
       <c r="BS82" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CC82" t="s">
         <v>10</v>
       </c>
       <c r="CD82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">
@@ -3357,7 +3432,7 @@
         <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BO83" t="s">
         <v>5</v>
@@ -3366,16 +3441,16 @@
         <v>7</v>
       </c>
       <c r="BS83" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BT83" t="s">
         <v>10</v>
       </c>
       <c r="BU83" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CD83" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84">
@@ -3386,7 +3461,7 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BO84" t="s">
         <v>5</v>
@@ -3395,16 +3470,16 @@
         <v>7</v>
       </c>
       <c r="BT84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BU84" t="s">
         <v>10</v>
       </c>
       <c r="BV84" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CE84" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85">
@@ -3415,7 +3490,7 @@
         <v>68</v>
       </c>
       <c r="C85" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BP85" t="s">
         <v>5</v>
@@ -3424,16 +3499,16 @@
         <v>7</v>
       </c>
       <c r="BT85" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BU85" t="s">
         <v>10</v>
       </c>
       <c r="BV85" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CE85" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86">
@@ -3444,7 +3519,7 @@
         <v>72</v>
       </c>
       <c r="C86" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BP86" t="s">
         <v>5</v>
@@ -3453,10 +3528,19 @@
         <v>7</v>
       </c>
       <c r="BU86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BV86" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="BW86" t="s">
+        <v>11</v>
+      </c>
+      <c r="BX86" t="s">
+        <v>11</v>
+      </c>
+      <c r="BY86" t="s">
+        <v>11</v>
       </c>
       <c r="BZ86" t="s">
         <v>10</v>
@@ -3471,10 +3555,10 @@
         <v>10</v>
       </c>
       <c r="CD86" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CF86" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87">
@@ -3485,7 +3569,7 @@
         <v>76</v>
       </c>
       <c r="C87" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BQ87" t="s">
         <v>5</v>
@@ -3494,7 +3578,7 @@
         <v>7</v>
       </c>
       <c r="BV87" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CD87" t="s">
         <v>10</v>
@@ -3506,7 +3590,7 @@
         <v>10</v>
       </c>
       <c r="CG87" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88">
@@ -3517,7 +3601,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BQ88" t="s">
         <v>5</v>
@@ -3526,13 +3610,13 @@
         <v>7</v>
       </c>
       <c r="BW88" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CG88" t="s">
         <v>10</v>
       </c>
       <c r="CH88" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89">
@@ -3543,7 +3627,7 @@
         <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BR89" t="s">
         <v>5</v>
@@ -3552,16 +3636,16 @@
         <v>7</v>
       </c>
       <c r="BW89" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BX89" t="s">
         <v>10</v>
       </c>
       <c r="BY89" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CH89" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90">
@@ -3572,7 +3656,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BR90" t="s">
         <v>5</v>
@@ -3581,16 +3665,16 @@
         <v>7</v>
       </c>
       <c r="BX90" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY90" t="s">
         <v>10</v>
       </c>
       <c r="BZ90" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CI90" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91">
@@ -3601,7 +3685,7 @@
         <v>68</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS91" t="s">
         <v>5</v>
@@ -3613,10 +3697,10 @@
         <v>10</v>
       </c>
       <c r="BY91" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CI91" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
@@ -3627,7 +3711,7 @@
         <v>72</v>
       </c>
       <c r="C92" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS92" t="s">
         <v>5</v>
@@ -3636,10 +3720,19 @@
         <v>7</v>
       </c>
       <c r="BY92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BZ92" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="CA92" t="s">
+        <v>11</v>
+      </c>
+      <c r="CB92" t="s">
+        <v>11</v>
+      </c>
+      <c r="CC92" t="s">
+        <v>11</v>
       </c>
       <c r="CD92" t="s">
         <v>10</v>
@@ -3654,10 +3747,10 @@
         <v>10</v>
       </c>
       <c r="CH92" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CJ92" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
@@ -3668,7 +3761,7 @@
         <v>76</v>
       </c>
       <c r="C93" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BT93" t="s">
         <v>5</v>
@@ -3677,7 +3770,7 @@
         <v>7</v>
       </c>
       <c r="BZ93" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CH93" t="s">
         <v>10</v>
@@ -3689,7 +3782,7 @@
         <v>10</v>
       </c>
       <c r="CK93" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94">
@@ -3700,7 +3793,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BT94" t="s">
         <v>5</v>
@@ -3709,22 +3802,22 @@
         <v>7</v>
       </c>
       <c r="CA94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CB94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CC94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CD94" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CK94" t="s">
         <v>10</v>
       </c>
       <c r="CL94" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
@@ -3735,7 +3828,7 @@
         <v>84</v>
       </c>
       <c r="C95" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BV95" t="s">
         <v>5</v>
@@ -3744,16 +3837,16 @@
         <v>7</v>
       </c>
       <c r="CD95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CE95" t="s">
         <v>10</v>
       </c>
       <c r="CF95" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CL95" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
@@ -3764,7 +3857,7 @@
         <v>88</v>
       </c>
       <c r="C96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BV96" t="s">
         <v>5</v>
@@ -3773,16 +3866,16 @@
         <v>7</v>
       </c>
       <c r="CE96" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CF96" t="s">
         <v>10</v>
       </c>
       <c r="CG96" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CM96" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
@@ -3793,7 +3886,7 @@
         <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CG97" t="s">
         <v>5</v>
@@ -3811,10 +3904,10 @@
         <v>10</v>
       </c>
       <c r="CL97" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CM97" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
@@ -3825,7 +3918,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CG98" t="s">
         <v>5</v>
@@ -3834,7 +3927,7 @@
         <v>7</v>
       </c>
       <c r="CI98" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CL98" t="s">
         <v>10</v>
@@ -3846,7 +3939,7 @@
         <v>10</v>
       </c>
       <c r="CO98" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
@@ -3857,7 +3950,7 @@
         <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CH99" t="s">
         <v>5</v>
@@ -3869,10 +3962,10 @@
         <v>10</v>
       </c>
       <c r="CK99" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CO99" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100">
@@ -3883,7 +3976,7 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CH100" t="s">
         <v>5</v>
@@ -3892,10 +3985,10 @@
         <v>10</v>
       </c>
       <c r="CK100" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CP100" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101">
@@ -3906,7 +3999,7 @@
         <v>108</v>
       </c>
       <c r="C101" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CI101" t="s">
         <v>5</v>
@@ -3915,16 +4008,16 @@
         <v>7</v>
       </c>
       <c r="CK101" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CL101" t="s">
         <v>10</v>
       </c>
       <c r="CM101" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CP101" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102">
@@ -3935,7 +4028,7 @@
         <v>112</v>
       </c>
       <c r="C102" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="CI102" t="s">
         <v>5</v>
@@ -3944,19 +4037,19 @@
         <v>7</v>
       </c>
       <c r="CK102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CL102" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CM102" t="s">
         <v>10</v>
       </c>
       <c r="CN102" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CQ102" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103">
@@ -3967,7 +4060,7 @@
         <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="CJ103" t="s">
         <v>5</v>
@@ -3976,19 +4069,19 @@
         <v>7</v>
       </c>
       <c r="CL103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CM103" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CN103" t="s">
         <v>10</v>
       </c>
       <c r="CO103" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CQ103" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104">
@@ -3999,7 +4092,7 @@
         <v>120</v>
       </c>
       <c r="C104" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CJ104" t="s">
         <v>5</v>
@@ -4008,19 +4101,19 @@
         <v>7</v>
       </c>
       <c r="CM104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CN104" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CO104" t="s">
         <v>10</v>
       </c>
       <c r="CP104" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CR104" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105">
@@ -4031,7 +4124,7 @@
         <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CK105" t="s">
         <v>5</v>
@@ -4040,19 +4133,19 @@
         <v>7</v>
       </c>
       <c r="CN105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CO105" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CP105" t="s">
         <v>10</v>
       </c>
       <c r="CQ105" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CR105" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106">
@@ -4063,7 +4156,7 @@
         <v>128</v>
       </c>
       <c r="C106" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="CK106" t="s">
         <v>5</v>
@@ -4072,19 +4165,19 @@
         <v>7</v>
       </c>
       <c r="CO106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CP106" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CQ106" t="s">
         <v>10</v>
       </c>
       <c r="CR106" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CS106" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107">
@@ -4095,7 +4188,7 @@
         <v>132</v>
       </c>
       <c r="C107" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="CL107" t="s">
         <v>5</v>
@@ -4104,16 +4197,16 @@
         <v>7</v>
       </c>
       <c r="CP107" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CQ107" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CR107" t="s">
         <v>10</v>
       </c>
       <c r="CS107" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108">
@@ -4124,7 +4217,7 @@
         <v>136</v>
       </c>
       <c r="C108" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="CL108" t="s">
         <v>5</v>
@@ -4133,16 +4226,16 @@
         <v>7</v>
       </c>
       <c r="CQ108" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CR108" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CS108" t="s">
         <v>10</v>
       </c>
       <c r="CT108" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109">
@@ -4153,7 +4246,7 @@
         <v>140</v>
       </c>
       <c r="C109" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="CM109" t="s">
         <v>5</v>
@@ -4162,21 +4255,21 @@
         <v>7</v>
       </c>
       <c r="CR109" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CS109" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CT109" t="s">
         <v>10</v>
       </c>
       <c r="CU109" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="112">
@@ -4184,7 +4277,7 @@
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="113">
@@ -4192,15 +4285,15 @@
         <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B114" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="115">
@@ -4208,39 +4301,55 @@
         <v>10</v>
       </c>
       <c r="B115" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B118" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B119" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>38</v>
+      </c>
+      <c r="B120" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>11</v>
+      </c>
+      <c r="B121" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
